--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -679,6 +679,12 @@
     <t>FLORIDINA ORANGE 350</t>
   </si>
   <si>
+    <t>20141623</t>
+  </si>
+  <si>
+    <t>IDM AIR BDD 6X500ML</t>
+  </si>
+  <si>
     <t>20026226</t>
   </si>
   <si>
@@ -805,19 +811,13 @@
     <t>FRUIT TEA FREEZE 350</t>
   </si>
   <si>
-    <t>20130354</t>
-  </si>
-  <si>
-    <t>LARISST JSMN TEA 350</t>
+    <t>20060210</t>
+  </si>
+  <si>
+    <t>IDM TEH HJAU MLT 330</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20060210</t>
-  </si>
-  <si>
-    <t>IDM TEH HJAU MLT 330</t>
   </si>
   <si>
     <t>20077509</t>
@@ -3667,10 +3667,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>34</v>
@@ -3690,7 +3690,7 @@
         <v>37</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>34</v>
@@ -3710,7 +3710,7 @@
         <v>37</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>34</v>
@@ -3730,7 +3730,7 @@
         <v>37</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>34</v>
@@ -3750,7 +3750,7 @@
         <v>37</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>34</v>
@@ -3770,7 +3770,7 @@
         <v>37</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>34</v>
@@ -3790,10 +3790,10 @@
         <v>37</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3810,7 +3810,7 @@
         <v>37</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>109</v>
@@ -3830,7 +3830,7 @@
         <v>37</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>109</v>
@@ -3850,10 +3850,10 @@
         <v>37</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3870,7 +3870,7 @@
         <v>37</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>34</v>
@@ -3890,10 +3890,10 @@
         <v>37</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3910,7 +3910,7 @@
         <v>37</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3927,13 +3927,13 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
@@ -3950,7 +3950,7 @@
         <v>70</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>34</v>
@@ -3970,7 +3970,7 @@
         <v>70</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>34</v>
@@ -3990,7 +3990,7 @@
         <v>70</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>34</v>
@@ -4010,7 +4010,7 @@
         <v>70</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>34</v>
@@ -4030,7 +4030,7 @@
         <v>70</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>34</v>
@@ -4050,7 +4050,7 @@
         <v>70</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>34</v>
@@ -4070,7 +4070,7 @@
         <v>70</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>34</v>
@@ -4090,18 +4090,18 @@
         <v>70</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>266</v>
+        <v>34</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B125" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
@@ -4113,7 +4113,7 @@
         <v>33</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4133,7 +4133,7 @@
         <v>37</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4153,7 +4153,7 @@
         <v>70</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4313,7 +4313,7 @@
         <v>27</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
         <v>30</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4993,7 +4993,7 @@
         <v>18</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
